--- a/assets/dcf/Cluck & Pluck - Solutions.xlsx
+++ b/assets/dcf/Cluck & Pluck - Solutions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pdwho\Dropbox\Courses\Teaching\Financial Analytics\Course\6 - Discounted Cash Flow &amp; Real Options\4 - Exercises\2 - Case\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA865848-7B73-4F0E-9BC9-AB075F23929A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35FC7F5D-87A9-423F-A938-C8F729E8C49A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10876" firstSheet="1" activeTab="2" xr2:uid="{6394BC74-EAE9-47A1-8528-22ED1E30B107}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10876" firstSheet="1" activeTab="1" xr2:uid="{6394BC74-EAE9-47A1-8528-22ED1E30B107}"/>
   </bookViews>
   <sheets>
     <sheet name="CB_DATA_" sheetId="3" state="veryHidden" r:id="rId1"/>
@@ -347,12 +347,6 @@
     <t>After the first year, you will gain a better understanding about the growth prospects of the business.</t>
   </si>
   <si>
-    <t>For years 2 through 5, the sales growth rate is assumed to be Normally distributed with mean 0% and standard deviation 3%. It assumed there is a singleshort-run growth for the restaurant (i.e. the growth rate for year 2 will be the same as the growth rates for years 3, 4 and 5).</t>
-  </si>
-  <si>
-    <t>After year 5, you assume the free cash flows will continue to grow indefintely at the same growth rate as the short-run sales growth rate.</t>
-  </si>
-  <si>
     <t>DCF Analysis</t>
   </si>
   <si>
@@ -365,31 +359,37 @@
     <t>㜸〱敤㕢㙢㤴㕣㔵㤵扥愷扡敥敤㍡搵慦捡〳㑣〰㐳㠱扣㍢㌴摤㠴っ〱〹㐹愷㍢㥤㌴㈴改㈴㥤〴ㄹ挴愶扡敡㔶扡㐸㍤㐲摤㕢改㙥㐰㜱慤㔹捥ㄲ㕤ち㐶ㄸ挴〱㐱ㅤ㔱㤰挷ㅡ㘰㄰㝣㡣㈰戸昰ㄱ㜵㕣愲㙢㕣挲㈸挲捣㠸㌲㄰㘷晥㌰戳ㅣ㌳摦户敦扤搵昵敡敡愴つ㙢昲挳㤳搴扥晢扣捦搹㝢㥦㝤昶搹攷戴愱っ挳㌸㠴挰㉦㐳㤸挸㐹愳搳㡥㙢攷㝡〶ち搹慣㥤㜴㌳㠵扣搳搳㕦㉣㈶愶㌷㘵ㅣ户〵〵慣戱っ昲ㅤ㜳捣挹㕣㙦㐷挶昶搹㐵〷㠵㑣挳㠸㐴㜴㠸慤昸扦㔸㄰搱慣愵㤹慣㔱捡搰ㄶ㐰㝢㉢挰㡥㠱㜵㈳攳搷愲㤳㔱户㔰戴㤷挷㜷㜹㑤慤敥敢敢改敢㔹搹㝢攱昹㍤扤换攳〳愵慣㕢㉡摡慢昳㜶挹㉤㈶戲换攳㕢㑢攳搹㑣昲㜲㝢㝡㐷㘱㡦㥤㕦㙤㡦昷慥ㄸ㑦㕣戰慡敦㠲㤵㉢搳ㄷ㕤戴慡㍤㠲㤶户っ慣摢㕡戴搳捥搱㙡㔳戳捤㤱㠱㜵㍤㕢㙣昷㘸戵ㄹ㐵㥢㘸㜲戰㤰㑢㘴昲㐷愹㔱㤳愴㕥㌱㘸㈷㌳攴㠹㙤ㄷ㌳昹摤㍤ㄸ㜶ㄵ愱ㄱ扢戰㘷〸ㄴ㑦㈶ㅣ㜷挰捥㘶户摢㘹戲愳㍤㐷㥡搹㐵㍢㥦戴㥤捥摣晡愹愴㥤昵戳㥤㐸㙥㔷愲戸㈵㤱戳挳㐴扡㜲ㅥ摦㠶㔳㜶摥捤戸搳ㅤ戹㥤㡥扤㍤㤱摦㙤戳㠸㤹摢㔰捡愴挲㘱ㄵづㅢ㉤㘷㌶ㅡ㡣昰愶㘷愸㤸ㅣ㤸㐸ㄴ㕤㠹㤱㙢㝤㡤捡㔶㐸㠸っ扣㙡㔸ㅣ㜶扣愶ㄶ搹㌴㥡挹㕤㙥ㄷ昳㜶㤶㥤㤰㜹摤㌵㠵㠴㈶ㅥ改换挴〹㘶㐳挶愸㌶㝦ㄹ㜰㉡散㐵户ㄱ戴〳㔸ㅤ〰㉤㕢戶敥搲㥤㑣敡〲㔰攱㠳㔸㐶㤵㔵㔸㍡㌴㤶〸㡤㡤㠷挶㤲愱戱㔴㘸捣づ㡤愵㐳㘳扢㐳㘳ㄳ愱戱㑣㘸散摡搰搸ㅥ㤴〹㐲愴戵㌵攴㠷㠵搶昹㉢愳昷㍥㍦昰昱慤㔷扢㤱㡤晦戸㐲㜱攵挸ㄲ㕡〰㐴㉦〴戰ㄶ〱㉣挴㄰攲㤳攷挵户摢㠹㙣㝣㘴㉦㔷慡㕥捣ㄲ挷〱㈸昵㕢㡣㠸愳㍡敤㠹㥢㈷挷㑥扡㘴昳敤改户㥥扡昹㥥㠱敦㤹㕣㠳㉢ㅢ㤱愳㤶搲晤㡥㔳捡㐹扢扥ㄴ㤰㐷㍡㌷攸戸㕢ㄳ挵㥣㜳㜴挵〵挲㌲㤷扣昴㍢戹户㕦㕥搰挹㔱㤱ㄷ敢ㅤ㈰搶搲㉤㠵㘲づ㍡㙢戳㥤挸慦敥㕤㍥敡愶〶敤㝤慢㝢㝢㝡㔷攸㈵愴攵㔲〰敢〴㠰昶搱㐴搶㜶攲ㅢ㡡㠵㐹㜷㐲㥦挸扣㤳〰㤴㝡挵攷攲㕦晦㙣挱㘹搷摦昸㡤㉤㝦昵㥡㤵㝤㌳晦搸㈶㐵㈵㑡㑥㕡换〰㑥慣散愷慦户户摣搵㡡摥㕥㝤㌲ち攸㌸㡢㥥〲搰㜶愵㥤㈸挶晢攲摦晡㑡扣㑦㥦捡慣㜷〱㈸昵愲摦搱昲㠳㈷㉥㜹昴㠶扢㠷ㅦ㝥攷搶攱㐳昹㐷ㅦ㘹㍦ㅤ搹摢晣挵㌰㔸㑣㑣㐲愳捣㈸㉢㘸㘸晥㥢㕢㑢㐳㐹愷㔷愶㉦㑣昷昵愵㔶昶㈶㔶㈴㑣㉥㤰挳搵つ㤴敡昶昴ㄵ㤹㝣慡㌰㈹捡愲㍤㍤㤴挹扡㜶㔱㈲㕤㘹㝣㍣㠵㈷昱㡥昴晡㈹散ㄴ㐹㑦慦㉣㑥て搸㐵ㄷㅡ搶㥤㥥ㄱ㥥㤳搶㈵ㅣ㝢㈶摡敤户扤慥㔰捡愷㥣ㄳㅢ㘷㡥扡〹搷㍥愱㌶㙦愶㤱扡㙡愳搰扥戶㈳㐳㕡㔶㕢㙤㔷㈲㕢戲晢愷㌲㕥昶㍢㙢戲愱㠷ぢ攳戳攷づㄵ敤敢捡戹㜵㈳敡挷㥥扤㑦摡慥㥢愵㤷攵㡤㉢㍥㌰㔱㜰散扣っ慦㍢户㌵㤳摣㘳ㄷ㐷㙤敥昸㜶㑡愶㝡ㅣ戳晣捤愰㝢㈴㡦㠹㐲扤愷㑥慤㑣㈵愱敤㝣捡㑥㘱扣㝢㐱攵改ㅤ㠹昱慣㝤㝣㔵ㄱ慦㑦㘴㉣慤㑡ㅥ㉡㈴㑢捥㐰㈱敦ㄶぢ搹敡㥣晥搴扥〴㌶愰搴收㐲捡づ㑢㌰㍣愸㡣㤶ㄶ愵㡣戳ㅡ愹㉥戶敤㔰搷㔷〸〹戵㔵昳挲ㄵ㐲挴挲つ昷㠸㜲换㐰㉡㠴㡣攵捦㙥㍡㤲㑡㈱㘴改摥愶愵ㅢ〸㈹㉢㉤愹㕥㜸㍤摢挱ㅦ昰㈱㙢㜳㔵㠶㑥㥢扤挹ㄹ戹㥣㘳愴ㄵ㕣愱㠱挷搲㑤㠸㈶捤㤶㘵敦敤㉤ㅣち㉤昲㘷扦㝥ㅦ捣㡣㡤㠹㝣㉡㙢ㄷ㥢㥡愷㡡㈳搲㘷㄰㥣㐹㜰ㄶ挱搹〴攷〰㤸㍦㠵㡥㥢㤵愲摣㘵搵㤴㥡㌶㈷㌳㈹㜷挲㥡戰㌳扢㈷㕣愴挱慣㡤㐴㐸敥㌸㝥晦㠲摦㈰㔴敦㌳戲ㅦ㉦㐷㑣㥦㑢搰〳㄰㡤ㅡ搶㜹昸ㅡ㔶㔴昷昲搳挷㐴愱㔸㝣挷昴㕥㍢慡㑣㥡て㐷㙥攴搰㡥搶㘲㔳挱攸㜵捣ㅣ㑣㌷愷愵愵ㄱ㈱㌶㈶㥣〹㤷㙢戰㘹愶㤸㌳攷戳搱ㄵ〰敤ㄷ〰㙣搹㘸㘷戱㠲㡦㤶扤㙣搲㌲㥡搳㉥愳㈵㜳㝣㙥㜴㍡㥦㥣㈸ㄶ昲㌸㑣っ㈶摣㐴㝦ㄲ挶愷愳ㄲ㔶㙥㔳㘱愰攴㕡戹㡤ㄹ㝣摡㜳摢敤扤㜶挲ㅤ㠰㠶㜶㍢㜲㥢㘰戸㡡ちㅤ㑥㑤㤹㌹捦收ㅣ戴㥤愴愶㜱㍡っ㡤㌴㘵〱㠳㡡㙤捦㔱挷搸㔳㉥㥢㙥捤挱㙥㠱㈴㘹ㄴ敡㤶㕡ㅥ挶㥡ㅤ㤲ㄶ搴㡥晡㌱戴㄰ㄳ戴愲㤵㌶㐹昰㕡㤲戳づ㌶㑦搸㘷㘱ㅦ搶㉥㥥㥤㙥㈶敢昴昸攴敤ㄹ㉣攰昰㘲换㜱㡡㘴户㉣挸㤶搵㤴㔹戵㙢㥣搶敤㐸㜲摣㙢ㄶ㐳㠱挹㔰摡㑢㡢攵㘸戵挳戶っ扤ㄲ攰㥥摦㍦昰敥搳敦㝥攴㤰晦扤〹慢㐷㠲愶〱慣㈹敡㡣攲㈳㐱慦挲㈷摡㉣捦愴愹摣㔰挹捥㘲㠸搳扥㘹捦㘱戶㍢㡡戶㥣㉣㈲ㄲ挱㕡敡挸㕤㔱㈸敥ㄹ㉦ㄴ昶㤰昹㥤ㄲ㜳㈶㙣摢愵戹摥收㥦㑥㠸㉢愵㕡㕡慡っ昳ち扢㥥㠶扥㜵〹㐰㐷㝦㌶ㅢて㕡㜴慣搵㐸㙡挱㘶㘲㕤ち攴摣挱㡣㤳愴搸搹愹昸〰搶㔷㝣㈸㕢㤸㡣昷攷ㄳ搹㘹㈷攳挴捦㡤敦戰㜳㝢戳戰つ㝡愶戲捥㤴㝡〶㈴愱搹扤晦戸㡥ㅦ慡ㅦ㕤㍡㝣昷攰敤㐳㕤慦晦昸㑣昵戴㥦㔱㘷摥搳慡㤷挳㐵㍦㄰扤㡥㘰㠰㘰㤰㘰㍤㠰晡㉡慡㔲㜷㍤ぢ㑤昰㌵〸摢㡣〶摡挰㌲ㅢ〹㠶〱愰㠱㠴㉤㔰㐰㤷㌳㑤ㄴ㤰㔲㕣㘷搴㍣㝡㌳挱ㄶ〰㐵㡢㡡㙢搴搰㈳〰戳㌲㥡挷㡣㝡㐶㙦㐷㙡㔴㌷挹㔳㍣㠱㤰搹㥡挴搵㈴愷㈶㈹搵ㄷ㝤ㅡ搴ㄱ攷㍥㍦愳敥戰㐲㌳戹㠹㤹㔸㜵㈴㠸愱㙣㤵㤹㔸㘷〰㜹搶挱㥦捤扣㘳捥捣慢㌶昱捥㤹挳慥愹㌱昲㘶摤搲晦㙣㈴㌵昲攱㜹㐶搲㔵㕣㡦㝦攷㉢ㄶ攰搵㐱㕦㡤戸㝥ㅦ挱ㄸ㐰㠵㘲㐹㜸㔱挵愳慢㈸㤵㜱ㄶ㑡〲㤸㍣戶㌶摦昴戱㕣愹ㄶ挲昴㈱㜴攴〶敤㜴〲捥㍤搹愸㔵攲晦㜳ㅦて挳昵㔹戱㠹㌷㥦〴挶捥㍤搲慡㌵晦慢晤㑥昰㠶愵㌶搸㜹ㅡ㝥捥搱摣㥥㡦收㌶慦㔳㤸㐷㄰捣扦㠵㌰ㅣ晥㥣㐰㉥愳㜵ㅦ㙤慣戱㌱㈳挲ㄹ㌲㐵搳㤹㔱扦㘳㑣㈰㌵摡㉣㑦搱摢㔱摥㌱慣ㅣ㘲㉤昴挴挸慥昱㠹搹㜶㡤㕢晤㡣㍡攷〸㕤ㅥ攲㘰戹づ㠸晡昸慣㔲敥㈰㕢搳挸搷㈵㠰ち㈹㥦昴愲㉡㡥慦㐸昹ㄴ㄰㍤つ愰㑥〵㄰〷捤昵㐰㠲愰㍥㠴㍥㐸㐰㈱挲㈹㐸慥㈷挲〷㤰ㅡ搵㑤昲ㄴ㍤㌱㘵㈲㘸ㄲ挱㈳挰つ晥㍣敢戶捤敢晤㡣㕡愷㡤挹㈳㔰慤㈵㉡㉥捦昲㜱戶㐲㠷搲㄰戰搲㍢昳ㄹ搷㘹㑢昷㤷摣挲㔰挶㠵㤰户愷〱㠰㑡㤵ㄳ攴ㅣ㔳㔱愹㍢扤㉢㘳㑦㔲扣㑦慥捦㠲㌷㜸愰攴戸〵㌱戲㤷搵攷てㄶ戶ㄴ㕣搸㔵戰㥢愶㑦㙢㤰敤攵㕣㌱㘱攷攱㡡㈸挲昲㥡慢㔰㘱敦㕥㍢搵㘰㡣愳㠵㔲㌱㘹ててㅥぢ捥っ攵㥤ㄶっㄸ愴㔰㌶敡昴搹㌷戹ち扡昳㐰ㅢ㠲ㄱ慢收㜹ㄶ㍥て昵つ晤㘱㐲昴〹ㄱ搷㌷〳㠵愴㥢㍣㈰㌷ㄷ㤱ち昷〸敤搳㘸ㅡ㙣昵搲㍡㝣晦摢㜰摥挹愴散愸ㅦ摢㥣挹㜷晡攸㐸挹慤捡㐹㑣㉤昲㜳㘰㘹㡦攴㘹㔲㈷㡡愹㘳㠱㉢㤸ㄸ㠲挷ㄲ㘵攱摦晣〸敤㌵㘳ㄸ〷㠳换戴㠳㌷㘱戱㝦〴挹愴昵㔹昸㌶㍣昸㤴㤷㈳㤰ち敦ㄲ㤵㐰〷挹㕤㑥㡥㌰㐶㌷戲㜰挱㜳㈴㜷㑡〹ㅢ〲㡥㑢㤸慣扤愸㍡㉡摢慡㑥昷㡦㍢㠵㙣挹戵㍢换㤸㉣㜴㥤摥㙥攳搰〲㑦㘱㝢ㄹ摢㥡㜴攱㑢㉤户㐷㉦攰戱挳㈱㔰㈴散㜳㐹〹㥦慣㈶挲㕢㍤〹慥愱㜹㜲ㄵ敡㍣㉤攱㡤㌵敡搳㜷㌲摣扦挶〸㤰㈸㠳㘱㥥㡤收㙢昷捤㙡㕤㕢改ち攴㑡㕡ㄴ㜸愸㍤つ㈷捡慢㍤㐸愳ㄷ慥㈳㉤㝡て慥㜶摥扣㜴㜱改㘴㜱㌹敡㘶㤲㠹㙣㜶扡㌳㍤㥣㑦㘶㑢㈹㝢㔳㘲摣捥〶㍡㥢㌷つ挷〶扦攴ㅡ搹攳㔵ㄳ扡昸㐴ㄹ挶㕤㜲攰㜸㥣户㥡㌳昴㐷㐱㔶搹㜲搱㐶㔴㝦っ㌱戲㠶㕥扦㈳昶扢搲㉢戰㜰收搶㐰慥㌵愱摡敡㤲愸搳攸㠸㉡扢㙥㘵挵㔵ㄴ摢㔴搸㔴㠰㕢㍤㔵㤱戴㌱攳㈵ㅤ㌳敢㑡搸㘴㔹搶㝣㌷ㄸ搰ち攱㘰搹ぢ昴收搴㙤昷扤晦㡥摦慣㌱㤴户㌸㤶㈳户搶㠵㔵戱㌸㘴敦ㄷ㈵挸挳㝢ㄷ㌵㤸㘷㌸散挸戸㔹扢㉤㉤昹㠲㐷戸㈴㐸捤搶昴㡥〹戸㠳〶㍢搲ㅢ㡡㤹㔴㌶㤳户㘹㠴攰㥡㠷㔷挹㥢散摤戸㤰搸㕡㜰㌲扣づ敤㐸敦㈸㈶昲捥㕥㝡晤㤲搳ぢ慢㘲挲㉣㌳扤㉥㤳挷〲昲晡㈴摥㤵ㅥ㥤㈸㑣攲敤㐳㈹㤷摦㤰搸敢ㅣㄳ㡣愲㔱改〵㙦㔵㠵㔴㈸愴㈲愱挸㝣昷㉡㜱搲㠹挱㑥㉦㜰㠸〰换㠵ぢ收㕣㘰㑤搶㉣㌹攵㕦〹㜱捤㜲㕣㔵户挰つ㥤搲攵挷㈳搴挳晡ㄶ搶戹ㄵ攰戲つ㍢㠷㘷㉥ㄲ晦愴㈷ㅦ㘶て摡㙢戲ㅤ㠸㘸㤴㙦㉤攸㥣敡昴挴㠵㘹㤴ㅥ㉤㕣㘷慣㔶〴愳㘹㈹㐳㘹挴づ捡攲㐴㠷攰㔴㙥挷攲㠷晡㠵㌳ㅥ㝡户搳㡢搰愴挳㝤慦攳攷つㄴ㜲戹〴挵㡢愲㌹ち摤㙤㐷挴扥㠶㌶搱㘹〰㤱㐱㍦㈹㌱㠵愴挴㤴㈴㘱㑢收㑤愴攰㙣慢戰㍢㔱捣戸ㄳ戹㑣㌲挲〸㙦ぢ㡦〹戹㠴〸昱搶㈴〸㈲㥣㌰㔶㙢㡦捦㥥慦ㅡ散敥挱昹㠱愴㈳晢㈱扤㈱搹挷搵㍣慦㜹㘰捤㡡挲搷晢搱㥡〹捦愸愱㈲敡㠶挵て㙦㜸昹㝡㜷㡤攲㘷昱挳㙦慥㠱㠸㡡㘴慢㕥ㄶ挰㑦㝦搲㐷ㄸ〹㔳昴㥢扡摦㜹㔷ㄲ摤㔴㐸愴㠶㜰愱㕣㈸戶晡㑦㤴㈲㘰㉤搵㑡㌱挶㉢㤷〱㕣㔵攲ち㜴ㅦ㙣攱㘲㠴〹愳戸捣〸昳戲挶昲㜸㐸〳搳㌰捤戶㐸愳扥㠶㠳戶㑥昳㕤搳㤵㉦慦㠶敢摡㝦㝤摢慡㌵ㄸㄴ愶㈵㜷㔰户〱搵户〳愸ㄵ〰㥣㑦㑤㠱扦㘱㠱㍢〰捣㤵〰戵慢㘴搶敢〹㌶㙥收㜸㙤ㄲ挹㜱㍡㌰㌹㉣㕣愶挰てづ㤲㔸㙤ㄱ㕥㕦攸㑦〱晣攰挰〱㍡㜸つ戵ち㈰攸㥦晥㠰㘸㤴挴搳㜷ㄲ㝣ㅡ㐰昵〳挸摤㥣㜷㈸戹ぢ搱攰㔰㜲㌷㔰攸ㅦ戵づ㕦ㅥ㑣㠲㔰㙤㑥㝦〶挹㉣㌵㠰㉦㑤㙡㌲㜴㉥昳㑣搱㡤㑥ㄳ捤搰昷㄰戰㙦戱ㄱ㍥ぢ㠴㡤搱挳㑥㍢愱㍡ㅣ扣愹敤昱㡢㕦㕡㝤搲换㤰㈰㑦㠰㌶愰〰㜷㌳㐳㍣摦搲㌷㘷㕢愱㍤搵㐶挴愹㐱昵攷〱搴㌰〰ㄵ㔳㔹㔰扦〰摣ㄳ㔴㍡㥢ㄸ㉡愶㠷ㄴ慦ㅦ㝡敥㤹慤敦昳ㄱ㐶搴㘶㠰㠰戸㐰㔱㔶戸晦㐵愰晡㑢〰㙡ぢ㐰㠳〲昷戳挰〳㉣㌰〲㐰〹搰㕦〶㈸㌳㙤㍢㈲㐱㌵戲换㘷摡㠳㉣昸㄰㠰㐹㍦攱ㄱ昸㘳㘹摥敡戲㙢㐰㑥㈸㌳㥥㠰㡥㜴攵挱㝦㔱摡昷〰㔴㥣昳㙢搲挴㌲㠶㜲㍥㠶㑥昱㤸ㅦ㠸ㄹ愸扡㜹㥢㑤㄰㐱攱㌷〴㤰慥㔶ㄱ㉣敢㘱㘰㡢扣愷㍣㜱搰挶㉤㘶挶㑢戴㘳搸愵㜰㐹昴㤵㉦㈷㜴捥㡡戰㍤〲㐴㡤〱㜸挲愶㍣慤昸昷㐸㤸㕢搸ㄲ慣㡢㥦㝥搴㐷㐴搸攸搲つ㠴〲㘸㈰㙣㡦〱搵㡦〳愸㈴㐰㠳〲晦挰〲㑦〰㤸㜴㉣搶㙥〳搵晥㔱摦㡢ㅡ㤶㌷㠵扣㠱㡤攰㌲㔳慥㙥㑤搱㤹㙤ㄵ㔷慥㤶㜷摢ㅡ㐱ㅤ㘰㌹挷ㅡ挵㠶㙡愷愲㥥㘴㔱㐷㜱㐱㠵㐲㘱散㉡㔶敤㙤㔱㕤户㙣㘲搴ㄶㅦ慥愲㥥戲扥〲戰㤸㝥㉦戴㍦㔶昵㄰㡢捡〲㉥戶戲㜵ぢ昷挹㔳㐸㌲愲㙡〲㌰愰〰ㅢ昱搷捤㔷㠱敡慦〱㈸㝡ㅥ戹㜶愸㙣〲㑥搳摤攸㜱晡敢挰づ㥢搳㜴㔰ち愷扦挱收㑡〰㔵㥣晥㈶ㄲ收收㌴㍤㥡挲改愷㝤㐴㌸㑤户㘶㌰つ愰〱愷㥦〱慡扦〵愰攸昲㙣㔰攰㔹ㄶ㜸㡥〵攸〵㈵户慤㙦〳㉣ち愸㔸昹挸慣〱ㄱ㥦㐷㔹㄰㤱ㅥ搱愰㜱㥥扡㝣㈲㝥〷愸晥㉥㠰昹㘱㠰挳昳㤳㔱㜷挵㉡㥣㤷攲㜷㕦㤰摥㔶㑡㘴昱㍥㜵〴㈷㘸㤷㐹挷㠲搹ㄴ昶晣ㄸ㜳捡愹㑣攱慡慢㈹㕤戵㌴愸㤶㘹㝦㙥㜲捤㌰㍦㍦㐷搴晣ぢ㐸昹攱昵㐲戹愹㜶晣㜳㈷㡡敡敦ㄳ㐲㥤摤㡣慦〸摡〱㈰㐱㔰ㅦ〱㔶㤷㙡㝥ㄴ愹㑤㡥ㅢ㌵㉥〲搶㕦㌴㘳ㅣ搱っ敥捥㐲㑤ㅥ挶愹攳〷散晥㘳㡤挶愰㙥〹㔲㝦攴㈳敤昸㥡晢〱㙡ㄵ㔸㥤ㅤㅢ㐶㈱㌸㍦㘱搱㡥扡搳㔹㥣㈲㠸㔲愱㜹ㄸ捤㈶㉦ㅢ㠳㉥ㄴ攱ㄶ〹搷㕥㔵㤶敢昲慡戲㙤㜱捤㙢㉦愹挶ㅣㅡ捣㘶㉦㔸㌴㙢晤㙡慥戰づ㠳昵㘳㠰挵㥢㌳挹㘲挱㈹愴摤昸㈸㑥挳㜱扥晦㑢挳㉦搲㙦昶愰挵㠶㝤㜲㘲攱㍣㥦㜲敦攳つ㑦㜴㑦扥㌰㤹㤷搱㤸づ㥦㐱ち㈷㕢㕢搹つ搷慤㠴㜷㠱扦㌱ㅡ搷慣慣㝦〲搰搱ㄲ愳㜵捡㄰扢摤晢ㅡ㌱㥡愳っ㌱㥡愴っ㕤㌴㈲搹㡡挵搸搱っ㌱㥡㥥ㄴ㑥敢〵㠰昶㠱㜵㘳戲戳㙣挷㔳㐱敢愷㐸㔹㠰㤴敡㜷散搶捦㤰摣㠹攴㡡㠳㙥㡣戶㉢㕢㤱挷摦晡㥦㠹搱捡㔱戴㕦愹愰愲敡っ搰㤱ぢ挸㕢〸扦㘰ㅡㄶ〲㙤㕡㈱搴㡢㐰㠲愰㘸挳搶愷搲㌴攵㘲搰㉦㌱晢戳つ换㝣㍥㐸晤愵㡦㤰㘰敡ぢ〰ㄴ㔶ㄵ挷〰㈸㈲挰つ敢㘵㠰㔹昹慥㤶愱ㄸ㜹㕦捤㍢摡㥢挲扢㔷㠰㠰㜷戴㉤ㄹ㘲㕦昲扥㐶散晥〰㜹挰㐷扡扥っ攴敤攱摤㠳㘸㤹昴戴㕥〵愸㘱㠹昵慦㐸慢收攷扦㈱愵㥥㥦戱㠷㤰捣㔶昴〲㠲㠵〴慦〱愸㐷〸ㄸ晢慤㡦戰㤰愲捤㈴戴㍣慥㤲㤶慦㈳㜵㜶㕡㉥㙡㐸换㐷㔱㐷㘸昹〶㄰搰㤲愶ㄳ㐳㡣收ㄳ㐳㡣戶ㄲ㐳㡣昶ㄲ㠳㐹换㘲捥㑤挱㌷㕥搸戶ㅡ㔷㐹㤵㔲㜶戸戵戵敥㌲愹㝡㠳㠰㕤㈳㥢〹户ㄲ换㈲㌴ㄷ㘰搸捤昵㝤㔰㠹㘴慡搷昷晡㈰㤲昵敦〱愲㌱ㅡ㍤ㅣ㤰昵㥦〰ぢ戱㝡㜰㜳ㅢ㍣愶ㄲ㙤㐸㜶㘹昲㔱㤳㑤㌱摡㐷㐲㥣㑢㤹戴㤴㘰〹挱㝦〳㈸戱㜱ㄸ晢ㅦ挶昰ㄳ捥搰挶ㄱ捥㤸ㄵ㥣搱攴っㄵ㤹㙡㘹挸㠴愷㤱㈹晤晣ㄱ〸㤸昰っ㍥っ㌱㕡㌶っ戱㘷扤慦ㄱ㝢捥㐷ㄴ㉤ㄳ㌲㐲㈹㌴㐹㈲㠹昴㜰㈰㥡㌶㘶㌴㐶攳㐴ㅡ攵㘴㜵捤捣扥ㅢ㘴捡捣攲㉣㜱㌲㠱㐶㔵昵㝤㘰昸ㅡ㍡ち挸㘶昹㡢ㅤ〰㘰㔰戲㐵〱搱攵ㄴ㐴㘲摣㤴愴扢㜶㔴敡㘸㌱愹㔷摦㍤晢捤㘱㠵摥敡挶敥㔹昵㌸㝢㍤ㅥ㕢㑦㠷㔰扦〵㥥〹捦挸づ㠷㉥㥥㕦㕢ㄴ愷〸㥡攲捦晣慦㍦ㅥ㍡昴㈷戴㐳㥡捣〸ㄸ㕢ㄴ㥡㜵㈲㕤㔱摢㜶攱㔷晢㤰散つ㜴搹昰㤵摤㝦昸ㄹ㜵慦散愸㤵搹㤳㕥っ㔸愶㝥愰㥡㤵攸㕤㘶〷㈹㈴㔴散㤷〰㐲晤攳㔱愹愳㐵扤㠲㌸㌹愰㕥㐳㌷㥣戶㡣㜴〹㐷㑡戵搲㘸愴慦捥㌶搲㔷晣㡣摡㈷㙦㌱慡㈴改㜴㤹搷㈹㔵㠸㜴晡㜲㘵愷㜱㘴㜶㜱ㄱ㥡昸㜱㈷愸〸〷搷昸㤱戵摥㌷攲㝦㘳㙢扢戸㘲愵挶搵敡㤴晤晤收慦㙥慡㝤晢攷搵㌰㡣㈷㤷㝤攸㜷摢㥥晣捣ㅡ挵㔵㌹㌳戱ㅣ㘲摥愳㠴ㄷ㘷㥢搸㉦晣㡣摡㔷ㄹ㌱慥㘸㤹搸ㄹ摥挴戸㉣㘵㘲㍦慦㥣搸㔹㥣ㄸ㔹㜵㘴ㄳ攳敡㥣㝢㘲㙢㙦㔹㡢㑥つ攳改攲㕡挵㐵搹㘸㘲㉦捣㌶戱㥦昸ㄹ戵慦㉤㘲㕣搰㌲戱ㅥ㈰晡㍣㠲㕥㠰愸挹㐵㍢㤷昳愴攲捦㐴㌸ㅡ㌳㑤㤵搹㤶昶㤲戹捥攴㝡㍤㉢搶㔷㍢㕣挴㐵晣愱挶㈶摣㝡挰㌱㡣扦㜲昳敤ㄷ摣㠶昰ㄸㅣ㌸㈱戵挴㔸搹㑡㡦ㄴ攱㤵㙣㑤て㍢戸㕢㐹㐵昰〴摡挵ㅦ捥攴㡦㠵㠳㄰散攱㌰㤷ㄹ搶㈳㕦㐴㠴ㅡ㥡愲愷㈳扢搶㘹㔹㜱㠱㌴㐳㡦攰ㄲ㌱㐴捦昲晣㡥㐱㔶ㅦ昸搵ㄵ晣㘵㘴㕣㙣㕦㈷愴㝥〸扥㡢戹昴扢昳㤷ㅥ㤲昱ㅡ㈱扣㥤㐷㔹敢〲〰扥ㄴ㔶㌲てㅣ昴昵㑡愴㜸ㅥ㤸昳㔸搴愴ㅡ慢㥤ㄸて〶㐳慣㔱昳户〶㙤㙤㥣敤攸㥤ㄷ昷晦敦㡡㤷晡㘳搴㔴㈲㔶ㄷ戲捤㔵〴ㄷ〱㐴ㄵ戵ㄱ㐵㑢㜳扣㈱昵敤㠶攳扢㠴〵㌸扥㤹戱㕤捡㈴づ㑢㠰愱愸戸㌸扥愰㐷㐵㡤挳㠶慤戵〰㠱㝦㈲㔵攱㠹ち慢㙦〶㥤ㄹㅦ㌴㘶㠸戱づ攵攵挱㤲攸㔸㠰愸ㅥ㘴㔲㐵㘷㜱挴搹㔹㄰ㄴ戵㠰㜴㌶〴愴㜱㘷㑦㌵散㙣㈳捡搷㜴㜶ㄹ㤳㉡㍡愳ㄲ愹敡慣〷〹愲㙢ㅥ㐷㤳搴摣㤷㘰ㅣ㤱㤰愵戸㕡㈵攳㌱㍦㘳戵㘴㈸挵ㄵ㉣ㄹ㡦晡ㄹ㔴慡㝡〴愹㈶㔹㝦搸㌲㠹戲昳㍤戵㙥㐵㕤㐵㠱㘲ㅢ㝡ㅢ㈰㠵㠶㍦㐵㤱㤰搱㍤㕣㌳ㅦ㡡㠹㘴㍣㔴㌳ㅦ㡡㡥㘴㍣㔸㌹㥦㥤㐸㔵ㄴㄵ捥㐹敦㘲㡣㔲㠲晦㠶扥〲戰摣㈱㌹㉣㘵摥挳㙣㌲ㄷ晦つ㝤愵㡦㌰愲挸ㄸ㈹昳㤷㑣㈵㑦㤸慣慦昲ㄱ㐶扡㐸挰㉢㠰㠴愶㔴昲㥡搴㌵搷扣搵ㄵ㡥㥦㄰㝥捦摡昶㍢㝦昵扤㕦敦㝦攱扤慢晦晤て㜷摤昵挲慢晢て晣攱敢攳慢㥦晦摣攷㥥扢散㥥〳扦㕥㤸扥㌷昴挴㕢㥢敥扤戱㙦捦㡤搷愵㜷㥥戳攱挶㉢慦摤搶户㜵㐱㜷㑢㑢㙢敢㤹㡢扥戳攴慣搸〷慦㝢㔲㍤昳昳㜷攴㤵㄰㡤摤扥ㄷ㍤㜱昸摣ㄵ㘲㈴㥥慣愵慢㠱攸昷〱㜴㠴扡㌸昹户㜵㉣㐲㑦㡥㘵っ㍤攱扦㙣搴㌱搲㔵挶㜲つ㄰㥤〰攸〸㈹㈱㉢㡢〶〶〸㜰㈳㐶昲㑡搱㈴㑢戵㈸㈱㙣㕤㈹ㄲ㔸㑡昱㘰づ㐳㤷㌳㤷㜸ㅡ㠸摥捤挴㤰攲挴㠵晦㥦昲昹扦づ敤㐴昰㈸㡣挴㤰㡣㍢晣㡣ㄸ㍢戸ㄶ愹㌱づ㕢ㅡ摡〳〴摤㜳挰㔲昴戶㥡㌶㌸〹挹昸㘴㘵ㅢ㜹愴攲㡣攲㘷㝤愲愶づ〷㉢㜵㙥慤捥㌰㌹敡㈶㙦〶㘶㔴㍥㙤㐵㥤攳㍢㈵㉡晦㘸㙥㝤扥攴晤搹㡦㤵攳㉤㝥㝥㠱敦㐰敡㉥㤷㔹㔸㑥㈹㤷敤㉣㈷㐹㥤愵摥㙤ㅣ晦㠸㡡㐵扡㘷ㅡ㍤慥㌶㐷捡㠳㍣愴㤰㜱敡散㠶㜴㌰㐰㌱㤸搵㘱ㄷ㡣㜸て戵慦〳㌵ㄸ㤴㉥㘳ㄲ㔵攴慢㌰戸〸㠴㘳㔰扡㡣㐹㔴㤱㠷戲ㅥㅤ㈰㡡㍣㤴昲㉥㄰㘹㐲㤷㌱㠹㉡昲㑢捡㤷㠰㤸散敥㌰〶换挶收改㤵摢㠷扡㡡㘳㘶㔷㝡㤲㌱ㄹ㈹㕡㉣㉦〳㥥㔶ㄵ挷㈹㘵愶㔹㠶愳挳晦㤹㌲㌴攷㤵㌴㔶㤹ち摣㔰搲㈸㔳㙦昰㉢戱愲㤲㘶㤸㕡戵搸㔸㠴㠴搳敦〷㠲戳ㄶ㍦㑤搴㝣昵㈳㌳㝡㐱㍡㜲摥㡤㠴戸㤹昰㠷㝡㘴㝣扤㔴㉥㘴㜲㜷㔵搱愸㤷㐴搸攵愱㘵昱㙣昳戳㈸捦㐷㉡㥢慤㤸つ㝦搰㍢换㥡㡢愷㈷㥡㠷㔷捡㤷换て㠰㍡㔱ㅥ㍣㤴㥥㐱㈵摥挵㌸㌵慦㝦㉣昹㈷晦㌸昲㥢㌵㙤晦〷㘸扦〹扦</t>
   </si>
   <si>
-    <t>If things go well, you will expand your operations and add 20 aditional restuarants.</t>
-  </si>
-  <si>
-    <t>At the end of year 5, you will assess how well your resturant business is performing.</t>
-  </si>
-  <si>
     <t>Terminal Value of Expansion</t>
   </si>
   <si>
-    <t>If you decide to expand, you will need to invest an additional $2,000 in working capital and $3,000 in new resturant buildings. These investments will be made in year 5.</t>
-  </si>
-  <si>
-    <t>The new restuarants will begin producing cash flows starting in year 6. To keep the analysis tractable, it is assumed the free cash flow of each new resturant will be the same as the free cash flow of the original resturant. For example, the FCF in year 6 of the expansion will equal the FCF in year 6 of the original resturant times 20.</t>
-  </si>
-  <si>
     <t>You will only invest in the expansion if it has a positive NPV.</t>
   </si>
   <si>
-    <t>Find the NPV of the resturant business that includes the option to expand if the business is performing well.</t>
-  </si>
-  <si>
     <t>Find the probability the NPV will be positive.</t>
   </si>
   <si>
     <t>Using Crystal Ball, plot the distribution of the NPV.</t>
+  </si>
+  <si>
+    <t>After year 5, you assume the free cash flows will continue to grow indefinitely at the same growth rate as the short-run sales growth rate.</t>
+  </si>
+  <si>
+    <t>At the end of year 5, you will assess how well your restaurant business is performing.</t>
+  </si>
+  <si>
+    <t>If things go well, you will expand your operations and add 20 additional restaurants.</t>
+  </si>
+  <si>
+    <t>If you decide to expand, you will need to invest an additional $2,000 in working capital and $3,000 in new restaurant buildings. These investments will be made in year 5.</t>
+  </si>
+  <si>
+    <t>The new restaurants will begin producing cash flows starting in year 6. To keep the analysis tractable, it is assumed the free cash flow of each new restaurant will be the same as the free cash flow of the original restaurant. For example, the FCF in year 6 of the expansion will equal the FCF in year 6 of the original restaurant times 20.</t>
+  </si>
+  <si>
+    <t>Find the NPV of the restaurant business that includes the option to expand if the business is performing well.</t>
+  </si>
+  <si>
+    <t>For years 2 through 5, the sales growth rate is assumed to be Normally distributed with mean 0% and standard deviation 3%. It assumed there is a single short-run growth for the restaurant (i.e. the growth rate for year 2 will be the same as the growth rates for years 3, 4 and 5).</t>
   </si>
 </sst>
 </file>
@@ -535,7 +535,7 @@
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -656,12 +656,6 @@
     <xf numFmtId="164" fontId="1" fillId="6" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -690,8 +684,6 @@
     </xf>
     <xf numFmtId="9" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="5" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -704,7 +696,6 @@
     <xf numFmtId="164" fontId="3" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -714,6 +705,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="3" builtinId="3"/>
@@ -1258,7 +1255,7 @@
         <v>53</v>
       </c>
       <c r="B27" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.45">
@@ -1316,7 +1313,7 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.45">
@@ -1371,7 +1368,7 @@
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A19" s="11" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.45">
@@ -1381,57 +1378,57 @@
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A23" s="11" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A27" s="11" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -1473,17 +1470,17 @@
       <c r="G1" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="I1" s="54" t="s">
+      <c r="I1" s="75" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="54"/>
+      <c r="J1" s="75"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A2" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="64">
+      <c r="B2" s="55"/>
+      <c r="C2" s="62">
         <v>1000</v>
       </c>
       <c r="D2" s="26">
@@ -1505,10 +1502,10 @@
       <c r="I2" t="s">
         <v>23</v>
       </c>
-      <c r="J2" s="67">
+      <c r="J2" s="65">
         <v>0</v>
       </c>
-      <c r="L2" s="78" t="s">
+      <c r="L2" s="73" t="s">
         <v>78</v>
       </c>
     </row>
@@ -1540,7 +1537,7 @@
       <c r="I3" t="s">
         <v>22</v>
       </c>
-      <c r="J3" s="62">
+      <c r="J3" s="60">
         <v>0.05</v>
       </c>
       <c r="L3" s="50" t="s">
@@ -1551,7 +1548,7 @@
       <c r="A4" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="58"/>
+      <c r="B4" s="56"/>
       <c r="C4" s="39">
         <f>C16*$J$4</f>
         <v>15</v>
@@ -1575,7 +1572,7 @@
       <c r="I4" t="s">
         <v>38</v>
       </c>
-      <c r="J4" s="62">
+      <c r="J4" s="60">
         <v>0.1</v>
       </c>
       <c r="L4" s="51" t="s">
@@ -1612,7 +1609,7 @@
       <c r="A6" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="59"/>
+      <c r="B6" s="57"/>
       <c r="C6" s="39">
         <f>B20*$J$6</f>
         <v>6</v>
@@ -1637,7 +1634,7 @@
       <c r="I6" t="s">
         <v>14</v>
       </c>
-      <c r="J6" s="62">
+      <c r="J6" s="60">
         <v>0.06</v>
       </c>
     </row>
@@ -1671,7 +1668,7 @@
       <c r="A8" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="60"/>
+      <c r="B8" s="58"/>
       <c r="C8" s="45">
         <f t="shared" ref="C8:G8" si="6">C7*$J$8</f>
         <v>8.6999999999999993</v>
@@ -1696,7 +1693,7 @@
       <c r="I8" t="s">
         <v>13</v>
       </c>
-      <c r="J8" s="62">
+      <c r="J8" s="60">
         <v>0.3</v>
       </c>
     </row>
@@ -1704,7 +1701,7 @@
       <c r="A9" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="61"/>
+      <c r="B9" s="59"/>
       <c r="C9" s="47">
         <f t="shared" ref="C9:G9" si="7">C7-C8</f>
         <v>20.3</v>
@@ -1738,14 +1735,14 @@
     </row>
     <row r="12" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A12" s="16"/>
-      <c r="B12" s="55" t="s">
+      <c r="B12" s="76" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="55"/>
-      <c r="D12" s="55"/>
-      <c r="E12" s="55"/>
-      <c r="F12" s="55"/>
-      <c r="G12" s="55"/>
+      <c r="C12" s="76"/>
+      <c r="D12" s="76"/>
+      <c r="E12" s="76"/>
+      <c r="F12" s="76"/>
+      <c r="G12" s="76"/>
       <c r="H12" s="11"/>
       <c r="I12" s="11"/>
       <c r="J12" s="22"/>
@@ -1804,7 +1801,7 @@
       <c r="I14" t="s">
         <v>21</v>
       </c>
-      <c r="J14" s="62">
+      <c r="J14" s="60">
         <v>0.03</v>
       </c>
     </row>
@@ -1839,7 +1836,7 @@
       <c r="I15" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="J15" s="62">
+      <c r="J15" s="60">
         <v>0.1</v>
       </c>
     </row>
@@ -1874,7 +1871,7 @@
       <c r="I16" t="s">
         <v>30</v>
       </c>
-      <c r="J16" s="66">
+      <c r="J16" s="64">
         <v>0.15</v>
       </c>
     </row>
@@ -1973,7 +1970,7 @@
       <c r="I20" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="J20" s="63">
+      <c r="J20" s="61">
         <v>0.4</v>
       </c>
     </row>
@@ -2009,7 +2006,7 @@
       <c r="I21" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="J21" s="63">
+      <c r="J21" s="61">
         <f>1-J20</f>
         <v>0.6</v>
       </c>
@@ -2110,7 +2107,7 @@
       <c r="A27" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B27" s="65">
+      <c r="B27" s="63">
         <v>0</v>
       </c>
       <c r="C27" s="26">
@@ -2339,11 +2336,11 @@
       <c r="G35" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="H35" s="71"/>
+      <c r="H35" s="67"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A36" s="68" t="s">
-        <v>101</v>
+      <c r="A36" t="s">
+        <v>97</v>
       </c>
       <c r="B36" s="48"/>
       <c r="C36" s="48"/>
@@ -2357,47 +2354,47 @@
       <c r="H36" s="36"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A37" s="74" t="s">
+      <c r="A37" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B37" s="70"/>
-      <c r="C37" s="70"/>
-      <c r="D37" s="70"/>
-      <c r="E37" s="70"/>
-      <c r="F37" s="70"/>
+      <c r="B37" s="66"/>
+      <c r="C37" s="66"/>
+      <c r="D37" s="66"/>
+      <c r="E37" s="66"/>
+      <c r="F37" s="66"/>
       <c r="G37" s="33">
         <f>100*20</f>
         <v>2000</v>
       </c>
       <c r="H37" s="36"/>
-      <c r="J37" s="56"/>
+      <c r="J37" s="54"/>
     </row>
     <row r="38" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A38" s="69" t="s">
+      <c r="A38" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B38" s="72"/>
-      <c r="C38" s="72"/>
-      <c r="D38" s="72"/>
-      <c r="E38" s="72"/>
-      <c r="F38" s="72"/>
-      <c r="G38" s="73">
+      <c r="B38" s="68"/>
+      <c r="C38" s="68"/>
+      <c r="D38" s="68"/>
+      <c r="E38" s="68"/>
+      <c r="F38" s="68"/>
+      <c r="G38" s="69">
         <f>150*20</f>
         <v>3000</v>
       </c>
       <c r="H38" s="36"/>
-      <c r="J38" s="56"/>
+      <c r="J38" s="54"/>
     </row>
     <row r="39" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A39" s="75" t="s">
+      <c r="A39" s="70" t="s">
         <v>71</v>
       </c>
-      <c r="B39" s="76"/>
-      <c r="C39" s="76"/>
-      <c r="D39" s="76"/>
-      <c r="E39" s="76"/>
-      <c r="F39" s="76"/>
-      <c r="G39" s="77">
+      <c r="B39" s="71"/>
+      <c r="C39" s="71"/>
+      <c r="D39" s="71"/>
+      <c r="E39" s="71"/>
+      <c r="F39" s="71"/>
+      <c r="G39" s="72">
         <f>MAX(G36-G37-G38,0)</f>
         <v>0</v>
       </c>
@@ -2412,7 +2409,7 @@
         <v>-250</v>
       </c>
       <c r="C40" s="37">
-        <f t="shared" ref="C40:G40" si="18">C33</f>
+        <f t="shared" ref="C40:F40" si="18">C33</f>
         <v>24.5</v>
       </c>
       <c r="D40" s="37">
@@ -2465,7 +2462,7 @@
       <c r="A46" t="s">
         <v>67</v>
       </c>
-      <c r="B46" s="79">
+      <c r="B46" s="74">
         <v>0.77</v>
       </c>
     </row>
@@ -2490,7 +2487,7 @@
       <c r="A50" t="s">
         <v>73</v>
       </c>
-      <c r="B50" s="79">
+      <c r="B50" s="74">
         <v>0.54</v>
       </c>
     </row>

--- a/assets/dcf/Cluck & Pluck - Solutions.xlsx
+++ b/assets/dcf/Cluck & Pluck - Solutions.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pdwho\Dropbox\Courses\Teaching\Financial Analytics\Course\6 - Discounted Cash Flow &amp; Real Options\4 - Exercises\2 - Case\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pdwho\Dropbox (Personal)\Courses\Teaching\Financial Analytics\Course\6 - Discounted Cash Flow &amp; Real Options\4 - Exercises\2 - Case\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35FC7F5D-87A9-423F-A938-C8F729E8C49A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98CA127A-A103-41AA-B4BA-AA775AE37B1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10876" firstSheet="1" activeTab="1" xr2:uid="{6394BC74-EAE9-47A1-8528-22ED1E30B107}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="13176" firstSheet="1" activeTab="2" xr2:uid="{6394BC74-EAE9-47A1-8528-22ED1E30B107}"/>
   </bookViews>
   <sheets>
     <sheet name="CB_DATA_" sheetId="3" state="veryHidden" r:id="rId1"/>
@@ -1147,17 +1147,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5894D0CC-EF0C-46B9-B369-B1EEB0FED917}">
   <dimension ref="A1:C31"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="36.59765625" customWidth="1"/>
+    <col min="1" max="2" width="36.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>40</v>
       </c>
@@ -1168,17 +1168,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>44</v>
       </c>
@@ -1186,17 +1186,17 @@
         <v>45</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B8">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="e">
         <f>CB_DATA_!#REF!</f>
         <v>#REF!</v>
@@ -1206,12 +1206,12 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>51</v>
       </c>
@@ -1219,17 +1219,17 @@
         <v>55</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>28</v>
       </c>
@@ -1237,12 +1237,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>52</v>
       </c>
@@ -1250,7 +1250,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>53</v>
       </c>
@@ -1258,7 +1258,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>54</v>
       </c>
@@ -1266,17 +1266,17 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B29" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B31" s="1" t="s">
         <v>54</v>
       </c>
@@ -1289,144 +1289,144 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{502FBBA9-AF17-499F-8A90-E73372ED630C}">
   <dimension ref="A1:A35"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>99</v>
       </c>
@@ -1440,17 +1440,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4551FB90-26B1-44C9-90FF-AB3D820DD8A7}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:L50"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.53125" bestFit="1" customWidth="1"/>
-    <col min="2" max="7" width="8.59765625" style="29" customWidth="1"/>
-    <col min="8" max="8" width="8.59765625" style="6" customWidth="1"/>
-    <col min="9" max="9" width="21.19921875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.19921875" style="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="7" width="8.5546875" style="29" customWidth="1"/>
+    <col min="8" max="8" width="8.5546875" style="6" customWidth="1"/>
+    <col min="9" max="9" width="21.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.5546875" style="15" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="24.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>5</v>
       </c>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="J1" s="75"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="17" t="s">
         <v>6</v>
       </c>
@@ -1509,7 +1509,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="18" t="s">
         <v>58</v>
       </c>
@@ -1544,7 +1544,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="20" t="s">
         <v>7</v>
       </c>
@@ -1579,7 +1579,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
         <v>8</v>
       </c>
@@ -1605,7 +1605,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="19" t="s">
         <v>9</v>
       </c>
@@ -1638,7 +1638,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="18" t="s">
         <v>10</v>
       </c>
@@ -1664,7 +1664,7 @@
         <v>28.28</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="44" t="s">
         <v>11</v>
       </c>
@@ -1697,7 +1697,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="46" t="s">
         <v>12</v>
       </c>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="J9"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B10" s="48"/>
       <c r="C10" s="48"/>
       <c r="D10" s="48"/>
@@ -1733,7 +1733,7 @@
       <c r="G10" s="48"/>
       <c r="I10" s="15"/>
     </row>
-    <row r="12" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="76" t="s">
         <v>24</v>
@@ -1747,7 +1747,7 @@
       <c r="I12" s="11"/>
       <c r="J12" s="22"/>
     </row>
-    <row r="13" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>3</v>
       </c>
@@ -1770,7 +1770,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>0</v>
       </c>
@@ -1805,12 +1805,11 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>15</v>
       </c>
       <c r="B15" s="40">
-        <f>C2*$J$15</f>
         <v>100</v>
       </c>
       <c r="C15" s="40">
@@ -1840,12 +1839,11 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="25" t="s">
         <v>1</v>
       </c>
       <c r="B16" s="41">
-        <f>C2*$J$16</f>
         <v>150</v>
       </c>
       <c r="C16" s="41">
@@ -1875,7 +1873,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>2</v>
       </c>
@@ -1905,7 +1903,7 @@
       </c>
       <c r="J17"/>
     </row>
-    <row r="18" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="16"/>
       <c r="B18" s="34"/>
       <c r="C18" s="34"/>
@@ -1915,7 +1913,7 @@
       <c r="G18" s="34"/>
       <c r="J18"/>
     </row>
-    <row r="19" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="5" t="s">
         <v>31</v>
       </c>
@@ -1938,7 +1936,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>37</v>
       </c>
@@ -1974,7 +1972,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="25" t="s">
         <v>4</v>
       </c>
@@ -2011,7 +2009,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>26</v>
       </c>
@@ -2044,7 +2042,7 @@
       </c>
       <c r="J22"/>
     </row>
-    <row r="25" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>70</v>
       </c>
@@ -2072,7 +2070,7 @@
       <c r="I25" s="21"/>
       <c r="J25" s="23"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>8</v>
       </c>
@@ -2103,7 +2101,7 @@
       <c r="I26" s="21"/>
       <c r="J26" s="23"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>20</v>
       </c>
@@ -2134,7 +2132,7 @@
       <c r="I27" s="21"/>
       <c r="J27" s="23"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>17</v>
       </c>
@@ -2163,7 +2161,7 @@
       </c>
       <c r="H28" s="29"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>18</v>
       </c>
@@ -2193,7 +2191,7 @@
       </c>
       <c r="H29" s="29"/>
     </row>
-    <row r="30" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="30" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="10" t="s">
         <v>19</v>
       </c>
@@ -2223,7 +2221,7 @@
       </c>
       <c r="H30" s="29"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>16</v>
       </c>
@@ -2263,7 +2261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="16" t="s">
         <v>27</v>
       </c>
@@ -2278,7 +2276,7 @@
       </c>
       <c r="H32" s="35"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="11" t="s">
         <v>28</v>
       </c>
@@ -2308,13 +2306,13 @@
       </c>
       <c r="H33" s="35"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D34" s="42"/>
       <c r="E34" s="42"/>
       <c r="F34" s="42"/>
       <c r="G34" s="42"/>
     </row>
-    <row r="35" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="35" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="5" t="s">
         <v>69</v>
       </c>
@@ -2338,7 +2336,7 @@
       </c>
       <c r="H35" s="67"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>97</v>
       </c>
@@ -2353,7 +2351,7 @@
       </c>
       <c r="H36" s="36"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>18</v>
       </c>
@@ -2369,7 +2367,7 @@
       <c r="H37" s="36"/>
       <c r="J37" s="54"/>
     </row>
-    <row r="38" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="38" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="10" t="s">
         <v>19</v>
       </c>
@@ -2385,7 +2383,7 @@
       <c r="H38" s="36"/>
       <c r="J38" s="54"/>
     </row>
-    <row r="39" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="39" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="70" t="s">
         <v>71</v>
       </c>
@@ -2400,7 +2398,7 @@
       </c>
       <c r="H39" s="36"/>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="11" t="s">
         <v>28</v>
       </c>
@@ -2430,7 +2428,7 @@
       </c>
       <c r="H40" s="35"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>25</v>
       </c>
@@ -2438,10 +2436,10 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C43" s="13"/>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="11" t="s">
         <v>66</v>
       </c>
@@ -2450,7 +2448,7 @@
         <v>-5.0000000000001137</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>74</v>
       </c>
@@ -2458,7 +2456,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>67</v>
       </c>
@@ -2466,7 +2464,7 @@
         <v>0.77</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="11" t="s">
         <v>68</v>
       </c>
@@ -2475,7 +2473,7 @@
         <v>-5.0000000000001137</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>72</v>
       </c>
@@ -2483,7 +2481,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>73</v>
       </c>
@@ -2507,7 +2505,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{683F6BDE-6A49-41F3-827F-7D83FCDB011D}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
